--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_1_9_full.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_1_9_full.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,891 +414,1349 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39400</v>
+        <v>38496</v>
       </c>
       <c r="B2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39583</v>
+        <v>38587</v>
       </c>
       <c r="B3">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D3">
-        <v>2009</v>
-      </c>
-      <c r="E3">
-        <v>1.265019766896436</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>39765</v>
+        <v>38678</v>
       </c>
       <c r="B4">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D4">
-        <v>2009</v>
-      </c>
-      <c r="E4">
-        <v>0.4618648366506939</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>39948</v>
+        <v>38770</v>
       </c>
       <c r="B5">
-        <v>2009</v>
-      </c>
-      <c r="C5">
-        <v>0.337821977117625</v>
+        <v>2006</v>
       </c>
       <c r="D5">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E5">
-        <v>1.858657482882586</v>
+        <v>-6.193667536543435</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>40130</v>
+        <v>38860</v>
       </c>
       <c r="B6">
-        <v>2009</v>
-      </c>
-      <c r="C6">
-        <v>0.348613976222456</v>
+        <v>2006</v>
       </c>
       <c r="D6">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E6">
-        <v>-2.340608900318997</v>
+        <v>2.464406476915149</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>40310</v>
+        <v>38953</v>
       </c>
       <c r="B7">
-        <v>2010</v>
-      </c>
-      <c r="C7">
-        <v>-1.890773121057054</v>
+        <v>2006</v>
       </c>
       <c r="D7">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E7">
-        <v>-3.246097549514837</v>
+        <v>-0.2750832359073363</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>40494</v>
+        <v>39044</v>
       </c>
       <c r="B8">
-        <v>2010</v>
-      </c>
-      <c r="C8">
-        <v>-0.1384957661262676</v>
+        <v>2006</v>
       </c>
       <c r="D8">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E8">
-        <v>1.659950937631938</v>
+        <v>2.706276173243394</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>40676</v>
+        <v>39135</v>
       </c>
       <c r="B9">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C9">
-        <v>1.891565607550105</v>
+        <v>0.3422125004754584</v>
       </c>
       <c r="D9">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E9">
-        <v>1.609625625600009</v>
+        <v>-0.4618041162320563</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>40862</v>
+        <v>39226</v>
       </c>
       <c r="B10">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C10">
-        <v>1.566479473280191</v>
+        <v>3.701949943713156</v>
       </c>
       <c r="D10">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E10">
-        <v>2.49756057493542</v>
+        <v>8.664288130980768</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>41044</v>
+        <v>39317</v>
       </c>
       <c r="B11">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C11">
-        <v>1.113165545862116</v>
+        <v>1.583284906622606</v>
       </c>
       <c r="D11">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="E11">
-        <v>1.609625625599986</v>
+        <v>-0.1980411904255241</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>41228</v>
+        <v>39408</v>
       </c>
       <c r="B12">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C12">
-        <v>0.7307568962937161</v>
+        <v>1.754772933362747</v>
       </c>
       <c r="D12">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="E12">
-        <v>1.029202372425875</v>
+        <v>0.2337942506875024</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>41409</v>
+        <v>39504</v>
       </c>
       <c r="B13">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C13">
-        <v>1.070385798714391</v>
+        <v>-0.4553950021398689</v>
       </c>
       <c r="D13">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E13">
-        <v>3.238605209600021</v>
+        <v>-2.007987251430488</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>41592</v>
+        <v>39595</v>
       </c>
       <c r="B14">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C14">
-        <v>0.8188188121642126</v>
+        <v>2.071027795385527</v>
       </c>
       <c r="D14">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E14">
-        <v>0.7004752402133052</v>
+        <v>5.125423150176811</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>41774</v>
+        <v>39686</v>
       </c>
       <c r="B15">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C15">
-        <v>1.384186838979828</v>
+        <v>1.828827313864267</v>
       </c>
       <c r="D15">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E15">
-        <v>2.777885851461526</v>
+        <v>1.448788027782344</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>41957</v>
+        <v>39777</v>
       </c>
       <c r="B16">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C16">
-        <v>0.9180054319587239</v>
+        <v>2.213924989827909</v>
       </c>
       <c r="D16">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E16">
-        <v>2.577405783391451</v>
+        <v>3.38639577408224</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>42137</v>
+        <v>39869</v>
       </c>
       <c r="B17">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C17">
-        <v>2.349355943833076</v>
+        <v>0.854379870434685</v>
       </c>
       <c r="D17">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="E17">
-        <v>2.436566844071941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>42321</v>
+        <v>39959</v>
       </c>
       <c r="B18">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C18">
-        <v>1.9846842782967</v>
+        <v>0.8793178469574725</v>
       </c>
       <c r="D18">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="E18">
-        <v>2.047428048848809</v>
+        <v>1.013743251195054</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>42503</v>
+        <v>40050</v>
       </c>
       <c r="B19">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C19">
-        <v>1.78642563555842</v>
+        <v>2.398276821552647</v>
       </c>
       <c r="D19">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="E19">
-        <v>1.694971351092267</v>
+        <v>1.895647644547482</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>42689</v>
+        <v>40141</v>
       </c>
       <c r="B20">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C20">
-        <v>1.755995812646982</v>
+        <v>2.534145137403332</v>
       </c>
       <c r="D20">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="E20">
-        <v>1.552965246735782</v>
+        <v>0.9842687475087653</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>42867</v>
+        <v>40233</v>
       </c>
       <c r="B21">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C21">
-        <v>1.331333081915509</v>
+        <v>0.07893141903445589</v>
       </c>
       <c r="D21">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="E21">
-        <v>1.216098605743343</v>
+        <v>-2.248605113324742</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>43053</v>
+        <v>40319</v>
       </c>
       <c r="B22">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C22">
-        <v>1.946965557828384</v>
+        <v>2.722714748034383</v>
       </c>
       <c r="D22">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="E22">
-        <v>0.232608152956959</v>
+        <v>4.356945153942826</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>43145</v>
+        <v>40414</v>
       </c>
       <c r="B23">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C23">
-        <v>0.5221702820068952</v>
+        <v>2.769077468485759</v>
       </c>
       <c r="D23">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E23">
-        <v>0.03619160485377471</v>
+        <v>2.134899126074541</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>43235</v>
+        <v>40505</v>
       </c>
       <c r="B24">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C24">
-        <v>1.282262557986469</v>
+        <v>2.088987206093629</v>
       </c>
       <c r="D24">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E24">
-        <v>1.784618024189033</v>
+        <v>3.612780209602295</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>43326</v>
+        <v>40598</v>
       </c>
       <c r="B25">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C25">
-        <v>1.238324979098082</v>
+        <v>2.4603689969251</v>
       </c>
       <c r="D25">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E25">
-        <v>1.281608622679209</v>
+        <v>2.244801469898805</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>43418</v>
+        <v>40687</v>
       </c>
       <c r="B26">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C26">
-        <v>1.064321453542272</v>
+        <v>2.432032972462994</v>
       </c>
       <c r="D26">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E26">
-        <v>-0.6993904531539141</v>
+        <v>5.259901377404663</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>43510</v>
+        <v>40871</v>
       </c>
       <c r="B27">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C27">
-        <v>0.5141202228481356</v>
+        <v>1.212532518945841</v>
       </c>
       <c r="D27">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="E27">
-        <v>0.8660061896410554</v>
+        <v>2.158842912663639</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>43600</v>
+        <v>40963</v>
       </c>
       <c r="B28">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C28">
-        <v>2.247109253368307</v>
+        <v>1.022966345475718</v>
       </c>
       <c r="D28">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E28">
-        <v>4.887093273600018</v>
+        <v>0.248215828547238</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>43691</v>
+        <v>41053</v>
       </c>
       <c r="B29">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C29">
-        <v>1.254519294658696</v>
+        <v>1.446803774865346</v>
       </c>
       <c r="D29">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E29">
-        <v>0.5495555957892195</v>
+        <v>0.7814544160914094</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>43783</v>
+        <v>41144</v>
       </c>
       <c r="B30">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C30">
-        <v>1.361817904277718</v>
+        <v>1.255320727877596</v>
       </c>
       <c r="D30">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E30">
-        <v>1.656460003703519</v>
+        <v>0.9830435428536122</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>43875</v>
+        <v>41236</v>
       </c>
       <c r="B31">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C31">
-        <v>0.6311979695890368</v>
+        <v>1.196784623675229</v>
       </c>
       <c r="D31">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="E31">
-        <v>0.07482640125564544</v>
+        <v>1.194043961570279</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>43966</v>
+        <v>41327</v>
       </c>
       <c r="B32">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C32">
-        <v>-4.247034401476779</v>
+        <v>1.528016940329691</v>
       </c>
       <c r="D32">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E32">
-        <v>-12.19860234240002</v>
+        <v>1.631895367953695</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>44068</v>
+        <v>41418</v>
       </c>
       <c r="B33">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C33">
-        <v>-9.171727975571519</v>
+        <v>0.3505172185931382</v>
       </c>
       <c r="D33">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E33">
-        <v>-35.38741355739603</v>
+        <v>-0.563230141139015</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>44159</v>
+        <v>41509</v>
       </c>
       <c r="B34">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C34">
-        <v>-4.352425014431327</v>
+        <v>0.8408213310559631</v>
       </c>
       <c r="D34">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E34">
-        <v>31.54369540926345</v>
+        <v>2.133826238299652</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>44251</v>
+        <v>41600</v>
       </c>
       <c r="B35">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C35">
-        <v>-7.006249401853603</v>
+        <v>0.4723812919182446</v>
       </c>
       <c r="D35">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="E35">
-        <v>-12.66856409363488</v>
+        <v>1.409680252440837</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>44341</v>
+        <v>41695</v>
       </c>
       <c r="B36">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C36">
-        <v>-8.773175314851734</v>
+        <v>0.686608012669998</v>
       </c>
       <c r="D36">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E36">
-        <v>-19.76612614777711</v>
+        <v>-0.07034203544042938</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>44432</v>
+        <v>41782</v>
       </c>
       <c r="B37">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C37">
-        <v>-2.664090177971856</v>
+        <v>0.673698994709393</v>
       </c>
       <c r="D37">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E37">
-        <v>11.21653887140452</v>
+        <v>1.713328878049047</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>44525</v>
+        <v>41968</v>
       </c>
       <c r="B38">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C38">
-        <v>-1.761645650979182</v>
+        <v>0.8777276606119377</v>
       </c>
       <c r="D38">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E38">
-        <v>22.41808675646531</v>
+        <v>2.372091426112677</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>44617</v>
+        <v>42059</v>
       </c>
       <c r="B39">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C39">
-        <v>0.421655805130472</v>
+        <v>1.311124869000135</v>
       </c>
       <c r="D39">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E39">
-        <v>-6.821105596638954</v>
+        <v>0.8468820036140912</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>44706</v>
+        <v>42146</v>
       </c>
       <c r="B40">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C40">
-        <v>3.555435198576862</v>
+        <v>2.178108891613229</v>
       </c>
       <c r="D40">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E40">
-        <v>-0.5376914776811237</v>
+        <v>2.743139622505342</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>44798</v>
+        <v>42241</v>
       </c>
       <c r="B41">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C41">
-        <v>5.042810166847067</v>
+        <v>1.986204709188399</v>
       </c>
       <c r="D41">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E41">
-        <v>3.311762715735989</v>
+        <v>1.113077264510842</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>44890</v>
+        <v>42332</v>
       </c>
       <c r="B42">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C42">
-        <v>5.20787683103745</v>
+        <v>2.290662253244125</v>
       </c>
       <c r="D42">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E42">
-        <v>4.121778551214828</v>
+        <v>4.595888802671189</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>44981</v>
+        <v>42423</v>
       </c>
       <c r="B43">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C43">
-        <v>-1.548915741813695</v>
+        <v>3.404941436848352</v>
       </c>
       <c r="D43">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E43">
-        <v>-3.955662492975198</v>
+        <v>4.043524422620237</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>45071</v>
+        <v>42514</v>
       </c>
       <c r="B44">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C44">
-        <v>-2.16280394131193</v>
+        <v>2.624199977941988</v>
       </c>
       <c r="D44">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E44">
-        <v>-4.829433539906869</v>
+        <v>1.891200602579302</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>45163</v>
+        <v>42606</v>
       </c>
       <c r="B45">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C45">
-        <v>-0.5369231962162102</v>
+        <v>3.854876966460385</v>
       </c>
       <c r="D45">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E45">
-        <v>0.09950561885605502</v>
+        <v>2.619782993551123</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>45254</v>
+        <v>42698</v>
       </c>
       <c r="B46">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C46">
-        <v>-0.9008525709169657</v>
+        <v>4.109910756223556</v>
       </c>
       <c r="D46">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E46">
-        <v>-0.9756765446554017</v>
+        <v>4.034930515252322</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>45345</v>
+        <v>42789</v>
       </c>
       <c r="B47">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C47">
-        <v>0.5260208614076722</v>
+        <v>2.993167714121348</v>
       </c>
       <c r="D47">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E47">
-        <v>0.9503229429644433</v>
+        <v>3.332445151470864</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>45436</v>
+        <v>42878</v>
       </c>
       <c r="B48">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C48">
-        <v>-0.244366674180263</v>
+        <v>1.714647081576248</v>
       </c>
       <c r="D48">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E48">
-        <v>-1.64927836088965</v>
+        <v>1.68734778233004</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>45534</v>
+        <v>42972</v>
       </c>
       <c r="B49">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C49">
-        <v>0.4276194584983628</v>
+        <v>2.016588334646352</v>
       </c>
       <c r="D49">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E49">
-        <v>-0.7585430378855618</v>
+        <v>2.393452018372799</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>45618</v>
+        <v>43062</v>
       </c>
       <c r="B50">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C50">
-        <v>0.2738544794132602</v>
+        <v>1.660180415270074</v>
       </c>
       <c r="D50">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E50">
-        <v>0.7075860014263302</v>
+        <v>0.02882935439718626</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>45713</v>
+        <v>43154</v>
       </c>
       <c r="B51">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C51">
-        <v>0.3683024421824888</v>
+        <v>1.862617018942903</v>
       </c>
       <c r="D51">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E51">
-        <v>0.3338002926567718</v>
+        <v>2.016119129497462</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>45800</v>
+        <v>43244</v>
       </c>
       <c r="B52">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C52">
-        <v>1.211873835667365</v>
+        <v>0.3317863932586596</v>
       </c>
       <c r="D52">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E52">
-        <v>1.973770215219273</v>
+        <v>-2.079831907815233</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>45891</v>
+        <v>43336</v>
       </c>
       <c r="B53">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C53">
-        <v>0.9621815008244994</v>
+        <v>1.195109139787243</v>
       </c>
       <c r="D53">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E53">
-        <v>0.3540813801726106</v>
+        <v>2.147346516455095</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
+        <v>43427</v>
+      </c>
+      <c r="B54">
+        <v>2018</v>
+      </c>
+      <c r="C54">
+        <v>1.0578868654878</v>
+      </c>
+      <c r="D54">
+        <v>2019</v>
+      </c>
+      <c r="E54">
+        <v>0.9137126991428879</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>43518</v>
+      </c>
+      <c r="B55">
+        <v>2019</v>
+      </c>
+      <c r="C55">
+        <v>4.205021405893228</v>
+      </c>
+      <c r="D55">
+        <v>2020</v>
+      </c>
+      <c r="E55">
+        <v>6.673045500176733</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>43608</v>
+      </c>
+      <c r="B56">
+        <v>2019</v>
+      </c>
+      <c r="C56">
+        <v>0.9803420752674485</v>
+      </c>
+      <c r="D56">
+        <v>2020</v>
+      </c>
+      <c r="E56">
+        <v>-1.060771667791693</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>43704</v>
+      </c>
+      <c r="B57">
+        <v>2019</v>
+      </c>
+      <c r="C57">
+        <v>1.749046390046982</v>
+      </c>
+      <c r="D57">
+        <v>2020</v>
+      </c>
+      <c r="E57">
+        <v>2.097038121371964</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>43791</v>
+      </c>
+      <c r="B58">
+        <v>2019</v>
+      </c>
+      <c r="C58">
+        <v>1.727536231884064</v>
+      </c>
+      <c r="D58">
+        <v>2020</v>
+      </c>
+      <c r="E58">
+        <v>2.928202216070308</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>43886</v>
+      </c>
+      <c r="B59">
+        <v>2020</v>
+      </c>
+      <c r="C59">
+        <v>2.306809538138754</v>
+      </c>
+      <c r="D59">
+        <v>2021</v>
+      </c>
+      <c r="E59">
+        <v>1.405193985066799</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>43976</v>
+      </c>
+      <c r="B60">
+        <v>2020</v>
+      </c>
+      <c r="C60">
+        <v>1.961124357427302</v>
+      </c>
+      <c r="D60">
+        <v>2021</v>
+      </c>
+      <c r="E60">
+        <v>0.8241099463141222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2">
+        <v>44068</v>
+      </c>
+      <c r="B61">
+        <v>2020</v>
+      </c>
+      <c r="C61">
+        <v>3.424327670918625</v>
+      </c>
+      <c r="D61">
+        <v>2021</v>
+      </c>
+      <c r="E61">
+        <v>5.715162389350259</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>44159</v>
+      </c>
+      <c r="B62">
+        <v>2020</v>
+      </c>
+      <c r="C62">
+        <v>3.806466406787412</v>
+      </c>
+      <c r="D62">
+        <v>2021</v>
+      </c>
+      <c r="E62">
+        <v>3.828815357603488</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>44251</v>
+      </c>
+      <c r="B63">
+        <v>2021</v>
+      </c>
+      <c r="C63">
+        <v>0.2968745741421142</v>
+      </c>
+      <c r="D63">
+        <v>2022</v>
+      </c>
+      <c r="E63">
+        <v>-2.009812043394155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2">
+        <v>44341</v>
+      </c>
+      <c r="B64">
+        <v>2021</v>
+      </c>
+      <c r="C64">
+        <v>2.091439143230134</v>
+      </c>
+      <c r="D64">
+        <v>2022</v>
+      </c>
+      <c r="E64">
+        <v>0.8024032016000104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>44432</v>
+      </c>
+      <c r="B65">
+        <v>2021</v>
+      </c>
+      <c r="C65">
+        <v>3.573519802127856</v>
+      </c>
+      <c r="D65">
+        <v>2022</v>
+      </c>
+      <c r="E65">
+        <v>6.778562662323795</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
+        <v>44525</v>
+      </c>
+      <c r="B66">
+        <v>2021</v>
+      </c>
+      <c r="C66">
+        <v>3.70707249977813</v>
+      </c>
+      <c r="D66">
+        <v>2022</v>
+      </c>
+      <c r="E66">
+        <v>-5.123155323668005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="2">
+        <v>44617</v>
+      </c>
+      <c r="B67">
+        <v>2022</v>
+      </c>
+      <c r="C67">
+        <v>2.475247231565136</v>
+      </c>
+      <c r="D67">
+        <v>2023</v>
+      </c>
+      <c r="E67">
+        <v>3.887763429212643</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="2">
+        <v>44706</v>
+      </c>
+      <c r="B68">
+        <v>2022</v>
+      </c>
+      <c r="C68">
+        <v>0.06634141764301216</v>
+      </c>
+      <c r="D68">
+        <v>2023</v>
+      </c>
+      <c r="E68">
+        <v>0.2741132537363411</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="2">
+        <v>44798</v>
+      </c>
+      <c r="B69">
+        <v>2022</v>
+      </c>
+      <c r="C69">
+        <v>3.992421056537521</v>
+      </c>
+      <c r="D69">
+        <v>2023</v>
+      </c>
+      <c r="E69">
+        <v>9.570988907138723</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="2">
+        <v>44890</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70">
+        <v>1.717176010541088</v>
+      </c>
+      <c r="D70">
+        <v>2023</v>
+      </c>
+      <c r="E70">
+        <v>0.39697463541013</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="2">
+        <v>44981</v>
+      </c>
+      <c r="B71">
+        <v>2023</v>
+      </c>
+      <c r="C71">
+        <v>1.076448324238388</v>
+      </c>
+      <c r="D71">
+        <v>2024</v>
+      </c>
+      <c r="E71">
+        <v>2.516883779494794</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2">
+        <v>45071</v>
+      </c>
+      <c r="B72">
+        <v>2023</v>
+      </c>
+      <c r="C72">
+        <v>-7.337826364178824</v>
+      </c>
+      <c r="D72">
+        <v>2024</v>
+      </c>
+      <c r="E72">
+        <v>-18.16135672608771</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2">
+        <v>45163</v>
+      </c>
+      <c r="B73">
+        <v>2023</v>
+      </c>
+      <c r="C73">
+        <v>-2.113649848251709</v>
+      </c>
+      <c r="D73">
+        <v>2024</v>
+      </c>
+      <c r="E73">
+        <v>-0.2006713809010963</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2">
+        <v>45254</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="C74">
+        <v>-1.789118639096632</v>
+      </c>
+      <c r="D74">
+        <v>2024</v>
+      </c>
+      <c r="E74">
+        <v>0.1752651703463615</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2">
+        <v>45345</v>
+      </c>
+      <c r="B75">
+        <v>2024</v>
+      </c>
+      <c r="C75">
+        <v>1.265895159907116</v>
+      </c>
+      <c r="D75">
+        <v>2025</v>
+      </c>
+      <c r="E75">
+        <v>1.396496092300681</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2">
+        <v>45436</v>
+      </c>
+      <c r="B76">
+        <v>2024</v>
+      </c>
+      <c r="C76">
+        <v>0.6782221590200921</v>
+      </c>
+      <c r="D76">
+        <v>2025</v>
+      </c>
+      <c r="E76">
+        <v>-1.69663885654836</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2">
+        <v>45534</v>
+      </c>
+      <c r="B77">
+        <v>2024</v>
+      </c>
+      <c r="C77">
+        <v>2.237405463944309</v>
+      </c>
+      <c r="D77">
+        <v>2025</v>
+      </c>
+      <c r="E77">
+        <v>3.906577894487895</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2">
+        <v>45618</v>
+      </c>
+      <c r="B78">
+        <v>2024</v>
+      </c>
+      <c r="C78">
+        <v>2.251694235954238</v>
+      </c>
+      <c r="D78">
+        <v>2025</v>
+      </c>
+      <c r="E78">
+        <v>2.166498632517477</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>45713</v>
+      </c>
+      <c r="B79">
+        <v>2025</v>
+      </c>
+      <c r="C79">
+        <v>3.146972940289072</v>
+      </c>
+      <c r="D79">
+        <v>2026</v>
+      </c>
+      <c r="E79">
+        <v>1.674460112552589</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2">
+        <v>45800</v>
+      </c>
+      <c r="B80">
+        <v>2025</v>
+      </c>
+      <c r="C80">
+        <v>1.643639910449846</v>
+      </c>
+      <c r="D80">
+        <v>2026</v>
+      </c>
+      <c r="E80">
+        <v>-1.36234030734832</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2">
+        <v>45891</v>
+      </c>
+      <c r="B81">
+        <v>2025</v>
+      </c>
+      <c r="C81">
+        <v>2.552678415604248</v>
+      </c>
+      <c r="D81">
+        <v>2026</v>
+      </c>
+      <c r="E81">
+        <v>2.939746115921049</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
         <v>45986</v>
       </c>
-      <c r="B54">
+      <c r="B82">
         <v>2025</v>
       </c>
-      <c r="C54">
-        <v>0.8976398032236155</v>
-      </c>
-      <c r="D54">
+      <c r="C82">
+        <v>2.593796720377783</v>
+      </c>
+      <c r="D82">
         <v>2026</v>
       </c>
-      <c r="E54">
-        <v>-0.6203510926954925</v>
+      <c r="E82">
+        <v>2.689732592045213</v>
       </c>
     </row>
   </sheetData>
